--- a/_note/Note.xlsx
+++ b/_note/Note.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Tantq\React\the-kanji-map\_note\convert\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tantq\src\kanji\_note\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5CF713-E00A-42CF-9044-A2A0A1CDE9DF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateCount="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Update Todos</t>
   </si>
@@ -55,171 +56,297 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Claude Code extension trong VS Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và muốn </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tự động chọn "Yes"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (không phải bấm Accept mỗi lần), thì có các chế độ sau:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Accept Edits</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Tự động chấp nhận các chỉnh sửa file trong project.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mở </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Settings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Ctrl + ,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tìm </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Claude Code: Initial Permission Mode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chọn </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>acceptEdits</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Khi đó Claude sẽ tự động áp dụng các chỉnh sửa file và một số lệnh an toàn mà không hỏi lại.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ki</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Claude Code extension trong VS Code</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>m tra chéo các âm Hán Vi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và muốn </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t hi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tự động chọn "Yes"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ế</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>m/đáng ng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (không phải bấm Accept mỗi lần), thì có các chế độ sau:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1. Accept Edits</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ờ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (tra qua T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> – Tự động chấp nhận các chỉnh sửa file trong project.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mở </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ừ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Settings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Ctrl + ,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tìm </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Claude Code: Initial Permission Mode</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Chọn </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>acceptEdits</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Khi đó Claude sẽ tự động áp dụng các chỉnh sửa file và một số lệnh an toàn mà không hỏi lại.</t>
-    </r>
+        <charset val="163"/>
+      </rPr>
+      <t>ể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n Hán Nôm hvdic.thivien.net):</t>
+    </r>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -228,7 +355,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -236,6 +363,20 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
     </font>
   </fonts>
   <fills count="2">
@@ -258,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -267,6 +408,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
@@ -548,10 +693,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="3.5703125" defaultRowHeight="15"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultColWidth="3.58203125" defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -615,6 +760,12 @@
       <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
